--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Yearly/yearly_combined_summary_costs_SOURCE.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Yearly/yearly_combined_summary_costs_SOURCE.xlsx
@@ -441,7 +441,7 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>891.35</v>
+        <v>877.39</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -450,34 +450,34 @@
         <v>34139.44</v>
       </c>
       <c r="F2">
-        <v>1166.92</v>
+        <v>1137.22</v>
       </c>
       <c r="G2">
-        <v>332.54</v>
+        <v>326.99</v>
       </c>
       <c r="H2">
-        <v>640.04</v>
+        <v>636.38</v>
       </c>
       <c r="I2">
-        <v>1151.09</v>
+        <v>1137.4</v>
       </c>
       <c r="J2">
         <v>22900</v>
       </c>
       <c r="K2">
-        <v>20411887.05</v>
+        <v>20092118.18</v>
       </c>
       <c r="L2">
-        <v>891.35</v>
+        <v>877.39</v>
       </c>
       <c r="M2">
-        <v>7.71</v>
+        <v>7.51</v>
       </c>
       <c r="N2">
-        <v>876.23</v>
+        <v>862.66</v>
       </c>
       <c r="O2">
-        <v>906.46</v>
+        <v>892.11</v>
       </c>
     </row>
     <row r="3">
@@ -490,43 +490,43 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>414.46</v>
+        <v>248.04</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>18930.48</v>
+        <v>18877.81</v>
       </c>
       <c r="F3">
-        <v>836.37</v>
+        <v>665.41</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>157.92</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>523.74</v>
+        <v>205.77</v>
       </c>
       <c r="J3">
-        <v>14172</v>
+        <v>22900</v>
       </c>
       <c r="K3">
-        <v>5873753.23</v>
+        <v>5680226.85</v>
       </c>
       <c r="L3">
-        <v>256.5</v>
+        <v>248.04</v>
       </c>
       <c r="M3">
-        <v>7.03</v>
+        <v>4.4</v>
       </c>
       <c r="N3">
-        <v>400.69</v>
+        <v>239.43</v>
       </c>
       <c r="O3">
-        <v>428.23</v>
+        <v>256.66</v>
       </c>
     </row>
     <row r="4">
@@ -539,7 +539,7 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>995.12</v>
+        <v>979.53</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -548,34 +548,34 @@
         <v>34139.44</v>
       </c>
       <c r="F4">
-        <v>1190.37</v>
+        <v>1159.21</v>
       </c>
       <c r="G4">
-        <v>343.14</v>
+        <v>333.66</v>
       </c>
       <c r="H4">
-        <v>694.04</v>
+        <v>679.87</v>
       </c>
       <c r="I4">
-        <v>1228.4</v>
+        <v>1207.77</v>
       </c>
       <c r="J4">
         <v>20512</v>
       </c>
       <c r="K4">
-        <v>20411887.05</v>
+        <v>20092118.18</v>
       </c>
       <c r="L4">
-        <v>995.12</v>
+        <v>979.53</v>
       </c>
       <c r="M4">
-        <v>8.31</v>
+        <v>8.09</v>
       </c>
       <c r="N4">
-        <v>978.83</v>
+        <v>963.67</v>
       </c>
       <c r="O4">
-        <v>1011.41</v>
+        <v>995.39</v>
       </c>
     </row>
     <row r="5">
@@ -588,43 +588,43 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>443.6</v>
+        <v>276.92</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>18930.48</v>
+        <v>18877.81</v>
       </c>
       <c r="F5">
-        <v>857.77</v>
+        <v>697.37</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>166.27</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>564.4299999999999</v>
+        <v>306.04</v>
       </c>
       <c r="J5">
-        <v>13241</v>
+        <v>20512</v>
       </c>
       <c r="K5">
-        <v>5873753.23</v>
+        <v>5680226.85</v>
       </c>
       <c r="L5">
-        <v>286.36</v>
+        <v>276.92</v>
       </c>
       <c r="M5">
-        <v>7.45</v>
+        <v>4.87</v>
       </c>
       <c r="N5">
-        <v>428.99</v>
+        <v>267.38</v>
       </c>
       <c r="O5">
-        <v>458.22</v>
+        <v>286.47</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Yearly/yearly_combined_summary_costs_SOURCE.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Yearly/yearly_combined_summary_costs_SOURCE.xlsx
@@ -441,43 +441,43 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>877.39</v>
+        <v>902.55</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>34139.44</v>
+        <v>33660.11</v>
       </c>
       <c r="F2">
-        <v>1137.22</v>
+        <v>1183.05</v>
       </c>
       <c r="G2">
-        <v>326.99</v>
+        <v>333.03</v>
       </c>
       <c r="H2">
-        <v>636.38</v>
+        <v>659.62</v>
       </c>
       <c r="I2">
-        <v>1137.4</v>
+        <v>1165.6</v>
       </c>
       <c r="J2">
         <v>22900</v>
       </c>
       <c r="K2">
-        <v>20092118.18</v>
+        <v>20668352.06</v>
       </c>
       <c r="L2">
-        <v>877.39</v>
+        <v>902.55</v>
       </c>
       <c r="M2">
-        <v>7.51</v>
+        <v>7.82</v>
       </c>
       <c r="N2">
-        <v>862.66</v>
+        <v>887.22</v>
       </c>
       <c r="O2">
-        <v>892.11</v>
+        <v>917.87</v>
       </c>
     </row>
     <row r="3">
@@ -490,16 +490,16 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>248.04</v>
+        <v>256.58</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>18877.81</v>
+        <v>19255.09</v>
       </c>
       <c r="F3">
-        <v>665.41</v>
+        <v>684.37</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -508,25 +508,25 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>205.77</v>
+        <v>219.76</v>
       </c>
       <c r="J3">
         <v>22900</v>
       </c>
       <c r="K3">
-        <v>5680226.85</v>
+        <v>5875791.56</v>
       </c>
       <c r="L3">
-        <v>248.04</v>
+        <v>256.58</v>
       </c>
       <c r="M3">
-        <v>4.4</v>
+        <v>4.52</v>
       </c>
       <c r="N3">
-        <v>239.43</v>
+        <v>247.72</v>
       </c>
       <c r="O3">
-        <v>256.66</v>
+        <v>265.45</v>
       </c>
     </row>
     <row r="4">
@@ -539,43 +539,43 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>979.53</v>
+        <v>1007.62</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>34139.44</v>
+        <v>33660.11</v>
       </c>
       <c r="F4">
-        <v>1159.21</v>
+        <v>1206.93</v>
       </c>
       <c r="G4">
-        <v>333.66</v>
+        <v>343.75</v>
       </c>
       <c r="H4">
-        <v>679.87</v>
+        <v>693.39</v>
       </c>
       <c r="I4">
-        <v>1207.77</v>
+        <v>1244.53</v>
       </c>
       <c r="J4">
         <v>20512</v>
       </c>
       <c r="K4">
-        <v>20092118.18</v>
+        <v>20668352.06</v>
       </c>
       <c r="L4">
-        <v>979.53</v>
+        <v>1007.62</v>
       </c>
       <c r="M4">
-        <v>8.09</v>
+        <v>8.43</v>
       </c>
       <c r="N4">
-        <v>963.67</v>
+        <v>991.1</v>
       </c>
       <c r="O4">
-        <v>995.39</v>
+        <v>1024.14</v>
       </c>
     </row>
     <row r="5">
@@ -588,16 +588,16 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>276.92</v>
+        <v>286.46</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>18877.81</v>
+        <v>19255.09</v>
       </c>
       <c r="F5">
-        <v>697.37</v>
+        <v>717.17</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -606,25 +606,25 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>306.04</v>
+        <v>323.26</v>
       </c>
       <c r="J5">
         <v>20512</v>
       </c>
       <c r="K5">
-        <v>5680226.85</v>
+        <v>5875791.56</v>
       </c>
       <c r="L5">
-        <v>276.92</v>
+        <v>286.46</v>
       </c>
       <c r="M5">
-        <v>4.87</v>
+        <v>5.01</v>
       </c>
       <c r="N5">
-        <v>267.38</v>
+        <v>276.64</v>
       </c>
       <c r="O5">
-        <v>286.47</v>
+        <v>296.27</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Yearly/yearly_combined_summary_costs_SOURCE.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Yearly/yearly_combined_summary_costs_SOURCE.xlsx
@@ -441,43 +441,43 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>902.55</v>
+        <v>898.23</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>33660.11</v>
+        <v>33733.18</v>
       </c>
       <c r="F2">
-        <v>1183.05</v>
+        <v>1154.66</v>
       </c>
       <c r="G2">
-        <v>333.03</v>
+        <v>299.37</v>
       </c>
       <c r="H2">
-        <v>659.62</v>
+        <v>598.75</v>
       </c>
       <c r="I2">
-        <v>1165.6</v>
+        <v>1196.45</v>
       </c>
       <c r="J2">
         <v>22900</v>
       </c>
       <c r="K2">
-        <v>20668352.06</v>
+        <v>20569422.91</v>
       </c>
       <c r="L2">
-        <v>902.55</v>
+        <v>898.23</v>
       </c>
       <c r="M2">
-        <v>7.82</v>
+        <v>7.63</v>
       </c>
       <c r="N2">
-        <v>887.22</v>
+        <v>883.27</v>
       </c>
       <c r="O2">
-        <v>917.87</v>
+        <v>913.1799999999999</v>
       </c>
     </row>
     <row r="3">
@@ -490,16 +490,16 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>256.58</v>
+        <v>252.64</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>19255.09</v>
+        <v>17932.74</v>
       </c>
       <c r="F3">
-        <v>684.37</v>
+        <v>666.02</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -508,25 +508,25 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>219.76</v>
+        <v>229.14</v>
       </c>
       <c r="J3">
         <v>22900</v>
       </c>
       <c r="K3">
-        <v>5875791.56</v>
+        <v>5785466.74</v>
       </c>
       <c r="L3">
-        <v>256.58</v>
+        <v>252.64</v>
       </c>
       <c r="M3">
-        <v>4.52</v>
+        <v>4.4</v>
       </c>
       <c r="N3">
-        <v>247.72</v>
+        <v>244.01</v>
       </c>
       <c r="O3">
-        <v>265.45</v>
+        <v>261.27</v>
       </c>
     </row>
     <row r="4">
@@ -539,43 +539,43 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>1007.62</v>
+        <v>1002.8</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>33660.11</v>
+        <v>33733.18</v>
       </c>
       <c r="F4">
-        <v>1206.93</v>
+        <v>1176.27</v>
       </c>
       <c r="G4">
-        <v>343.75</v>
+        <v>323.14</v>
       </c>
       <c r="H4">
-        <v>693.39</v>
+        <v>681.15</v>
       </c>
       <c r="I4">
-        <v>1244.53</v>
+        <v>1245.02</v>
       </c>
       <c r="J4">
         <v>20512</v>
       </c>
       <c r="K4">
-        <v>20668352.06</v>
+        <v>20569422.91</v>
       </c>
       <c r="L4">
-        <v>1007.62</v>
+        <v>1002.8</v>
       </c>
       <c r="M4">
-        <v>8.43</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="N4">
-        <v>991.1</v>
+        <v>986.7</v>
       </c>
       <c r="O4">
-        <v>1024.14</v>
+        <v>1018.9</v>
       </c>
     </row>
     <row r="5">
@@ -588,16 +588,16 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>286.46</v>
+        <v>282.05</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>19255.09</v>
+        <v>17932.74</v>
       </c>
       <c r="F5">
-        <v>717.17</v>
+        <v>697.8</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -606,25 +606,25 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>323.26</v>
+        <v>299.37</v>
       </c>
       <c r="J5">
         <v>20512</v>
       </c>
       <c r="K5">
-        <v>5875791.56</v>
+        <v>5785466.74</v>
       </c>
       <c r="L5">
-        <v>286.46</v>
+        <v>282.05</v>
       </c>
       <c r="M5">
-        <v>5.01</v>
+        <v>4.87</v>
       </c>
       <c r="N5">
-        <v>276.64</v>
+        <v>272.5</v>
       </c>
       <c r="O5">
-        <v>296.27</v>
+        <v>291.6</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Yearly/yearly_combined_summary_costs_SOURCE.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Yearly/yearly_combined_summary_costs_SOURCE.xlsx
@@ -441,43 +441,43 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>898.23</v>
+        <v>919.4299999999999</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>33733.18</v>
+        <v>33761.9</v>
       </c>
       <c r="F2">
-        <v>1154.66</v>
+        <v>1226.63</v>
       </c>
       <c r="G2">
-        <v>299.37</v>
+        <v>333.03</v>
       </c>
       <c r="H2">
-        <v>598.75</v>
+        <v>660.5</v>
       </c>
       <c r="I2">
-        <v>1196.45</v>
+        <v>1176.87</v>
       </c>
       <c r="J2">
         <v>22900</v>
       </c>
       <c r="K2">
-        <v>20569422.91</v>
+        <v>21054888.43</v>
       </c>
       <c r="L2">
-        <v>898.23</v>
+        <v>919.4299999999999</v>
       </c>
       <c r="M2">
-        <v>7.63</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="N2">
-        <v>883.27</v>
+        <v>903.54</v>
       </c>
       <c r="O2">
-        <v>913.1799999999999</v>
+        <v>935.3200000000001</v>
       </c>
     </row>
     <row r="3">
@@ -490,16 +490,16 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>252.64</v>
+        <v>264.54</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>17932.74</v>
+        <v>23276.65</v>
       </c>
       <c r="F3">
-        <v>666.02</v>
+        <v>719.8</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -508,25 +508,25 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>229.14</v>
+        <v>231.53</v>
       </c>
       <c r="J3">
         <v>22900</v>
       </c>
       <c r="K3">
-        <v>5785466.74</v>
+        <v>6057939.02</v>
       </c>
       <c r="L3">
-        <v>252.64</v>
+        <v>264.54</v>
       </c>
       <c r="M3">
-        <v>4.4</v>
+        <v>4.76</v>
       </c>
       <c r="N3">
-        <v>244.01</v>
+        <v>255.22</v>
       </c>
       <c r="O3">
-        <v>261.27</v>
+        <v>273.86</v>
       </c>
     </row>
     <row r="4">
@@ -539,43 +539,43 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>1002.8</v>
+        <v>1026.47</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>33733.18</v>
+        <v>33761.9</v>
       </c>
       <c r="F4">
-        <v>1176.27</v>
+        <v>1252.96</v>
       </c>
       <c r="G4">
-        <v>323.14</v>
+        <v>352.22</v>
       </c>
       <c r="H4">
-        <v>681.15</v>
+        <v>708.97</v>
       </c>
       <c r="I4">
-        <v>1245.02</v>
+        <v>1268.16</v>
       </c>
       <c r="J4">
         <v>20512</v>
       </c>
       <c r="K4">
-        <v>20569422.91</v>
+        <v>21054888.43</v>
       </c>
       <c r="L4">
-        <v>1002.8</v>
+        <v>1026.47</v>
       </c>
       <c r="M4">
-        <v>8.210000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="N4">
-        <v>986.7</v>
+        <v>1009.32</v>
       </c>
       <c r="O4">
-        <v>1018.9</v>
+        <v>1043.61</v>
       </c>
     </row>
     <row r="5">
@@ -588,16 +588,16 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>282.05</v>
+        <v>295.34</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>17932.74</v>
+        <v>23276.65</v>
       </c>
       <c r="F5">
-        <v>697.8</v>
+        <v>754.54</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -606,25 +606,25 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>299.37</v>
+        <v>326.82</v>
       </c>
       <c r="J5">
         <v>20512</v>
       </c>
       <c r="K5">
-        <v>5785466.74</v>
+        <v>6057939.02</v>
       </c>
       <c r="L5">
-        <v>282.05</v>
+        <v>295.34</v>
       </c>
       <c r="M5">
-        <v>4.87</v>
+        <v>5.27</v>
       </c>
       <c r="N5">
-        <v>272.5</v>
+        <v>285.01</v>
       </c>
       <c r="O5">
-        <v>291.6</v>
+        <v>305.66</v>
       </c>
     </row>
   </sheetData>
